--- a/backend/income_details.xlsx
+++ b/backend/income_details.xlsx
@@ -398,7 +398,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C2"/>
+  <dimension ref="A1:C6"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -413,18 +413,62 @@
     </row>
     <row r="2">
       <c r="A2" s="1">
-        <v>45732.29201388889</v>
+        <v>45751.29201388889</v>
       </c>
       <c r="B2" t="str">
-        <v>Salary</v>
+        <v xml:space="preserve">Đánh thắng người ta nên được tiền </v>
       </c>
       <c r="C2">
-        <v>5600</v>
+        <v>9999</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="1">
+        <v>45749.29201388889</v>
+      </c>
+      <c r="B3" t="str">
+        <v>cá sấu cho</v>
+      </c>
+      <c r="C3">
+        <v>1200</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="1">
+        <v>45742.686643946756</v>
+      </c>
+      <c r="B4" t="str">
+        <v>Donate</v>
+      </c>
+      <c r="C4">
+        <v>1600</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="1">
+        <v>45740.29201388889</v>
+      </c>
+      <c r="B5" t="str">
+        <v>Đẳng cấp</v>
+      </c>
+      <c r="C5">
+        <v>1553</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="1">
+        <v>45736.29201388889</v>
+      </c>
+      <c r="B6" t="str">
+        <v>Rồng bay rơi ra</v>
+      </c>
+      <c r="C6">
+        <v>1000</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:C2"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:C6"/>
   </ignoredErrors>
 </worksheet>
 </file>